--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104597_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104597_W16.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8216</v>
+        <v>11.0731</v>
       </c>
       <c r="E2" t="n">
-        <v>8.682399999999999</v>
+        <v>8.869400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1392</v>
+        <v>2.2037</v>
       </c>
       <c r="G2" t="n">
-        <v>9.545400000000001</v>
+        <v>9.5398</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6636</v>
+        <v>1.6739</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8818</v>
+        <v>7.866</v>
       </c>
       <c r="J2" t="n">
-        <v>8.782</v>
+        <v>8.7454</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3912</v>
+        <v>0.3825</v>
       </c>
       <c r="L2" t="n">
-        <v>8.3909</v>
+        <v>8.363</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7634</v>
+        <v>0.7944</v>
       </c>
       <c r="N2" t="n">
-        <v>1.2724</v>
+        <v>1.2914</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4309</v>
+        <v>-1.1692</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6657</v>
+        <v>-0.6394</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2123</v>
+        <v>4.417</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5733</v>
+        <v>2.7917</v>
       </c>
       <c r="F3" t="n">
-        <v>1.639</v>
+        <v>1.6253</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6585</v>
+        <v>2.6562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.798</v>
+        <v>0.7957</v>
       </c>
       <c r="I3" t="n">
         <v>1.8605</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1248</v>
+        <v>2.1111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1001</v>
+        <v>0.3055</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5175</v>
+        <v>0.4868</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0806</v>
+        <v>3.7067</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5809</v>
+        <v>2.8898</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4997</v>
+        <v>0.8169</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4061</v>
+        <v>2.4033</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5815</v>
+        <v>-1.5797</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9876</v>
+        <v>3.983</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1376</v>
+        <v>3.1025</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6735</v>
+        <v>-1.6934</v>
       </c>
       <c r="L4" t="n">
-        <v>4.8112</v>
+        <v>4.7959</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7316</v>
+        <v>-0.6992</v>
       </c>
       <c r="N4" t="n">
-        <v>0.092</v>
+        <v>0.1137</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8718</v>
+        <v>-1.2414</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0371</v>
+        <v>-0.7603</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8803</v>
+        <v>1.9101</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6872</v>
+        <v>2.6492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1931</v>
+        <v>-0.7392</v>
       </c>
       <c r="G5" t="n">
-        <v>0.485</v>
+        <v>2.9378</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5919</v>
+        <v>2.9494</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0769</v>
+        <v>-0.0116</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4543</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6998</v>
+        <v>2.4476</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1541</v>
+        <v>0.3724</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0307</v>
+        <v>0.1178</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1079</v>
+        <v>0.5018</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6221</v>
+        <v>-1.0764</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5939</v>
+        <v>-0.4392</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9718</v>
+        <v>-0.6372</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.935</v>
+        <v>1.8186</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5537</v>
+        <v>3.6376</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6186</v>
+        <v>-1.8191</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9264</v>
+        <v>3.9487</v>
       </c>
       <c r="H6" t="n">
-        <v>2.945</v>
+        <v>2.1537</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0186</v>
+        <v>1.795</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8321</v>
+        <v>4.932</v>
       </c>
       <c r="K6" t="n">
-        <v>2.459</v>
+        <v>1.365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3732</v>
+        <v>3.5671</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.9833</v>
       </c>
       <c r="N6" t="n">
-        <v>0.486</v>
+        <v>0.7887</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3918</v>
+        <v>-1.772</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0329</v>
+        <v>-1.3075</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.1955</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4764</v>
+        <v>-1.1121</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>1.639</v>
+        <v>1.405</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7317</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.181</v>
+        <v>1.81</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9726</v>
+        <v>1.4952</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7915</v>
+        <v>0.3148</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9409</v>
+        <v>0.5032</v>
       </c>
       <c r="H7" t="n">
-        <v>2.147</v>
+        <v>-0.5753</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7939</v>
+        <v>1.0786</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9579</v>
+        <v>0.4432</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3782</v>
+        <v>-0.7035</v>
       </c>
       <c r="L7" t="n">
-        <v>3.5797</v>
+        <v>1.1467</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.017</v>
+        <v>0.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7688</v>
+        <v>0.1281</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7858</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4952</v>
+        <v>-0.4553</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9471</v>
+        <v>-0.4656</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9043</v>
+        <v>0.4177</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0428</v>
+        <v>-0.8834</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4141</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5732</v>
+        <v>-0.0677</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5133</v>
+        <v>-0.0975</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0599</v>
+        <v>0.0297</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8753</v>
+        <v>-0.8736</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1818</v>
+        <v>-1.1805</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3065</v>
+        <v>0.3069</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.455</v>
+        <v>-0.4755</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6837</v>
+        <v>-1.6967</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2287</v>
+        <v>1.2211</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4203</v>
+        <v>-0.3981</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1801</v>
+        <v>0.5296</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8075</v>
+        <v>0.2203</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3726</v>
+        <v>0.3093</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3184</v>
+        <v>-0.2693</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1522</v>
+        <v>-0.3966</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1662</v>
+        <v>0.1273</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2461</v>
+        <v>-0.2426</v>
       </c>
       <c r="H9" t="n">
-        <v>0.287</v>
+        <v>0.2954</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5331</v>
+        <v>-0.538</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3639</v>
+        <v>-0.3732</v>
       </c>
       <c r="K9" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1178</v>
+        <v>0.1306</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1546</v>
+        <v>0.2009</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4386</v>
+        <v>0.2042</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.284</v>
+        <v>-0.0033</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1284</v>
+        <v>-2.897</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4424</v>
+        <v>-1.5062</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-1.3908</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3838</v>
+        <v>-1.581</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-3.3864</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3838</v>
+        <v>1.8053</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0365</v>
+        <v>-0.8658</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1874</v>
+        <v>-3.0551</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2239</v>
+        <v>2.1893</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4203</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1874</v>
+        <v>-0.3312</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6077</v>
+        <v>-0.384</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4952</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2969</v>
+        <v>-0.0185</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0162</v>
+        <v>0.2505</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2806</v>
+        <v>-0.2691</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7119</v>
+        <v>-2.966</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4189</v>
+        <v>-2.0514</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2929</v>
+        <v>-0.9145</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5823</v>
+        <v>-0.375</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3896</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8072</v>
+        <v>-0.375</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8425</v>
+        <v>0.0231</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0415</v>
+        <v>-0.2003</v>
       </c>
       <c r="L11" t="n">
-        <v>2.199</v>
+        <v>0.2234</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7398</v>
+        <v>-0.3981</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.348</v>
+        <v>0.2003</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3918</v>
+        <v>-0.5984</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8366</v>
+        <v>0.4577</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6956</v>
+        <v>0.4294</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.141</v>
+        <v>0.0283</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.5253</v>
+        <v>18.5355</v>
       </c>
       <c r="E12" t="n">
-        <v>18.5499</v>
+        <v>18.2812</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02429999999999977</v>
+        <v>0.2541000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>18.8748</v>
+        <v>18.9168</v>
       </c>
       <c r="H12" t="n">
-        <v>1.095799999999999</v>
+        <v>1.146199999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>17.7789</v>
+        <v>17.7707</v>
       </c>
       <c r="J12" t="n">
-        <v>20.6638</v>
+        <v>20.4628</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1121</v>
+        <v>-2.2199</v>
       </c>
       <c r="L12" t="n">
-        <v>22.7763</v>
+        <v>22.6828</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7891</v>
+        <v>-1.546</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2081</v>
+        <v>3.3661</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.9972</v>
+        <v>-4.912</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1341</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.3417</v>
+        <v>-11.3815</v>
       </c>
       <c r="R12" t="n">
-        <v>12.4759</v>
+        <v>12.5198</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.765499999999999</v>
+        <v>-3.7849</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3174999999999997</v>
+        <v>-0.3048000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.4481</v>
+        <v>-3.4804</v>
       </c>
       <c r="V12" t="n">
-        <v>2.2818</v>
+        <v>2.2652</v>
       </c>
       <c r="W12" t="n">
-        <v>9.545</v>
+        <v>9.504700000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.263100000000001</v>
+        <v>-7.2393</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2383</v>
+        <v>3.3586</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3947</v>
+        <v>4.4169</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1565</v>
+        <v>-1.0583</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5826</v>
+        <v>3.572</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1456</v>
+        <v>-2.1509</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7282</v>
+        <v>5.7229</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9564</v>
+        <v>5.9201</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6562</v>
+        <v>-1.6762</v>
       </c>
       <c r="L13" t="n">
-        <v>7.6126</v>
+        <v>7.5963</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3738</v>
+        <v>-2.3481</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.796</v>
+        <v>0.3297</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.747</v>
+        <v>0.3178</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.049</v>
+        <v>0.0119</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1074</v>
+        <v>0.9769</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5393</v>
+        <v>2.3413</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6467</v>
+        <v>-1.3644</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5787</v>
+        <v>-1.5735</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0593</v>
+        <v>-0.0494</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5194</v>
+        <v>-1.5241</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2965</v>
+        <v>1.2733</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5612</v>
+        <v>-0.5656</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8577</v>
+        <v>1.8388</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8752</v>
+        <v>-2.8467</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.3771</v>
+        <v>-3.3629</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7554999999999999</v>
+        <v>0.3227</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1693</v>
+        <v>0.6614</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5861</v>
+        <v>-0.3388</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1821</v>
+        <v>0.5003</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3337</v>
+        <v>0.2342</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1516</v>
+        <v>0.2661</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1518</v>
+        <v>-0.1489</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0157</v>
+        <v>1.0221</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1675</v>
+        <v>-1.171</v>
       </c>
       <c r="J15" t="n">
-        <v>0.839</v>
+        <v>0.8244</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1429</v>
+        <v>1.1376</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9908</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8961</v>
+        <v>-0.2126</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6775</v>
+        <v>-0.0863</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2187</v>
+        <v>-0.1264</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2917</v>
+        <v>-0.4475</v>
       </c>
       <c r="E16" t="n">
-        <v>1.287</v>
+        <v>-0.1406</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5786</v>
+        <v>-0.3069</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5141</v>
+        <v>-0.8249</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1223</v>
+        <v>0.5516</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3918</v>
+        <v>-1.3765</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9343</v>
+        <v>-0.2381</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6806</v>
+        <v>0.5516</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7463</v>
+        <v>-0.7896</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5798</v>
+        <v>-0.5868</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4417</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1381</v>
+        <v>-0.5868</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6346</v>
+        <v>0.1498</v>
       </c>
       <c r="T16" t="n">
-        <v>2.102</v>
+        <v>0.0975</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5326</v>
+        <v>0.0523</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>J. SASTRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7127</v>
+        <v>-0.764</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3713</v>
+        <v>-0.363</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3414</v>
+        <v>-0.401</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8213</v>
+        <v>-1.492</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5541</v>
+        <v>-0.8218</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3754</v>
+        <v>-0.6703</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2322</v>
+        <v>-0.3464</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5541</v>
+        <v>-0.376</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7864</v>
+        <v>0.0296</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5891</v>
+        <v>-1.1457</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.4458</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5891</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1183</v>
+        <v>0.2241</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1391</v>
+        <v>0.2111</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0209</v>
+        <v>0.013</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8685</v>
+        <v>-2.1688</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4722</v>
+        <v>-0.2804</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3963</v>
+        <v>-1.8885</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5001</v>
+        <v>-2.5228</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8284</v>
+        <v>-2.1388</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6717</v>
+        <v>-0.384</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3361</v>
+        <v>-0.9627</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3708</v>
+        <v>-1.7074</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0346</v>
+        <v>0.7447</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1639</v>
+        <v>-1.5601</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4576</v>
+        <v>-0.4314</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>-1.1287</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1364</v>
+        <v>0.7605</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0907</v>
+        <v>0.5732</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0457</v>
+        <v>0.1873</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0356</v>
+        <v>-2.8604</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6486</v>
+        <v>0.8847</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6842</v>
+        <v>-3.7451</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6152</v>
+        <v>-3.6419</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8565</v>
+        <v>-0.894</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7587</v>
+        <v>-2.7479</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.1358</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3902</v>
+        <v>-1.4391</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5311</v>
+        <v>-3.5061</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.0648</v>
+        <v>-4.0511</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8065</v>
+        <v>1.0091</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4548</v>
+        <v>0.7521</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3517</v>
+        <v>0.257</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0122</v>
+        <v>-3.1752</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8253</v>
+        <v>-2.1454</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8375</v>
+        <v>-1.0298</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0787</v>
+        <v>-2.9337</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6295</v>
+        <v>1.5308</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7081</v>
+        <v>-4.4645</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6157</v>
+        <v>-2.2078</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9067</v>
+        <v>0.1239</v>
       </c>
       <c r="L20" t="n">
-        <v>0.709</v>
+        <v>-2.3317</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6944</v>
+        <v>-0.7259</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7228</v>
+        <v>1.4069</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.4171</v>
+        <v>-2.1328</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.6293</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.083</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9491</v>
+        <v>-0.2219</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7462</v>
+        <v>0.0624</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2029</v>
+        <v>-0.2843</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2534</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0988</v>
+        <v>-4.1164</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9555</v>
+        <v>-1.436</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1433</v>
+        <v>-2.6803</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9311</v>
+        <v>-4.927</v>
       </c>
       <c r="H21" t="n">
-        <v>1.531</v>
+        <v>0.0228</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.4621</v>
+        <v>-4.9499</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1903</v>
+        <v>-1.9352</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1314</v>
+        <v>-0.3932</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.3218</v>
+        <v>-1.542</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7408</v>
+        <v>-2.9918</v>
       </c>
       <c r="N21" t="n">
-        <v>1.3995</v>
+        <v>0.416</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1404</v>
+        <v>-3.4078</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1411</v>
+        <v>0.1765</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.135</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3759</v>
+        <v>0.3115</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3393</v>
+        <v>-4.5929</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8924</v>
+        <v>-0.7512</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.447</v>
+        <v>-3.8417</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9324</v>
+        <v>-1.0936</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0202</v>
+        <v>1.6067</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.9525</v>
+        <v>-2.7003</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9235</v>
+        <v>1.5824</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3881</v>
+        <v>0.8749</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5354</v>
+        <v>0.7075</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0089</v>
+        <v>-2.6759</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4082</v>
+        <v>0.7319</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.4171</v>
+        <v>-3.4078</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4537</v>
+        <v>-4.0974</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.046</v>
+        <v>1.39</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6079</v>
+        <v>1.2191</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5619</v>
+        <v>0.171</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1154</v>
+        <v>-5.2459</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1917</v>
+        <v>-3.5594</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9237</v>
+        <v>-1.6865</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3341</v>
+        <v>-3.3306</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1658</v>
+        <v>0.1747</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.4999</v>
+        <v>-3.5053</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2179</v>
+        <v>-2.2283</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1162</v>
+        <v>-1.1023</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.1429</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1603</v>
+        <v>-0.193</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1685</v>
+        <v>0.0501</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.5254</v>
+        <v>-18.5353</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5219000000000014</v>
+        <v>-0.7988999999999988</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.0036</v>
+        <v>-17.7364</v>
       </c>
       <c r="G24" t="n">
-        <v>-18.8749</v>
+        <v>-18.9169</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0958</v>
+        <v>-1.146199999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-17.7789</v>
+        <v>-17.7709</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7892</v>
+        <v>1.5459</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.2081</v>
+        <v>-3.3661</v>
       </c>
       <c r="L24" t="n">
-        <v>4.996999999999998</v>
+        <v>4.911999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-20.664</v>
+        <v>-20.4627</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1121</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>-22.7761</v>
+        <v>-22.6825</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q24" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R24" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7654</v>
+        <v>3.784999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>3.448</v>
+        <v>3.4803</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3174999999999999</v>
+        <v>0.3046</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.2819</v>
+        <v>-2.2652</v>
       </c>
       <c r="W24" t="n">
-        <v>6.716799999999999</v>
+        <v>6.694599999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.998699999999999</v>
+        <v>-8.959899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104597_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104597_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.2393</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104597_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-8.959899999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
